--- a/plantillas/Reporte_Participacion.xlsx
+++ b/plantillas/Reporte_Participacion.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8823588-3C8A-444E-AAB8-0A2503A4E7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DE74EA-0F72-441A-A6E5-DFCB5A79EEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,8 @@
     <t>titulo 1</t>
   </si>
   <si>
-    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS (SICOVACC)</t>
+    <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
+SICOVACC 2026</t>
   </si>
 </sst>
 </file>
@@ -178,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -194,6 +195,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -519,36 +523,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="2:3" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="7"/>
+    </row>
+    <row r="3" spans="2:3" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7"/>
-    </row>
-    <row r="5" spans="2:3" ht="18" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="C3" s="8"/>
+    </row>
+    <row r="5" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="8"/>
     </row>
     <row r="6" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="8" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>3</v>
       </c>
     </row>
@@ -556,10 +560,10 @@
       <c r="C10" s="2"/>
     </row>
     <row r="11" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="10"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">

--- a/plantillas/Reporte_Participacion.xlsx
+++ b/plantillas/Reporte_Participacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DE74EA-0F72-441A-A6E5-DFCB5A79EEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4452903-3F48-4FD2-BDB6-E906EF7941F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
   </si>
   <si>
     <t>SISTEMA DE CÓMPUTO Y VALIDACIONES PARA LAS CONSULTAS CIUDADANAS
-SICOVACC 2026</t>
+SICOVACC</t>
   </si>
 </sst>
 </file>
